--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:43</t>
+    <t xml:space="preserve">2026-09-09 22:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:30</t>
+    <t xml:space="preserve">2026-09-12 19:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_o higgins.xlsx
@@ -36,102 +36,102 @@
     <t xml:space="preserve">O'Higgins</t>
   </si>
   <si>
+    <t xml:space="preserve">Nancagua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Cabras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requínoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mostazal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Codegua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Fernando</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coltauco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Estrella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peralillo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rengo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Vicente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa Cruz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchigüe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graneros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Litueche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Placilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coinco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pumanque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chépica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinta de Tilcoco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chimbarongo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olivar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malloa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navidad</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pichilemu</t>
   </si>
   <si>
-    <t xml:space="preserve">Las Cabras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requínoa</t>
+    <t xml:space="preserve">Pichidegua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doñihue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peumo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palmilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paredones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lolol</t>
   </si>
   <si>
     <t xml:space="preserve">Machalí</t>
   </si>
   <si>
-    <t xml:space="preserve">Rengo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Litueche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coltauco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chimbarongo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Codegua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Estrella</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marchigüe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Vicente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coinco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pichidegua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nancagua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peralillo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Placilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pumanque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mostazal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Graneros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chépica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doñihue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malloa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinta de Tilcoco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa Cruz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olivar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lolol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palmilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paredones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peumo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Fernando</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rancagua</t>
   </si>
   <si>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:46</t>
+    <t xml:space="preserve">2026-09-24 00:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -568,13 +568,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>6201</v>
+        <v>6305</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2968</v>
+        <v>873</v>
       </c>
     </row>
     <row r="3">
@@ -591,7 +591,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2873</v>
+        <v>718</v>
       </c>
     </row>
     <row r="4">
@@ -608,7 +608,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2783</v>
+        <v>685</v>
       </c>
     </row>
     <row r="5">
@@ -619,13 +619,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>6108</v>
+        <v>6110</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2338</v>
+        <v>616</v>
       </c>
     </row>
     <row r="6">
@@ -636,13 +636,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>6115</v>
+        <v>6102</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1931</v>
+        <v>564</v>
       </c>
     </row>
     <row r="7">
@@ -653,13 +653,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6203</v>
+        <v>6301</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1864</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8">
@@ -676,7 +676,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1780</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -687,13 +687,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>6205</v>
+        <v>6202</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1755</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10">
@@ -704,13 +704,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>6303</v>
+        <v>6307</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1571</v>
+        <v>386</v>
       </c>
     </row>
     <row r="11">
@@ -721,13 +721,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>6102</v>
+        <v>6115</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1363</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12">
@@ -738,13 +738,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>6202</v>
+        <v>6117</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="13">
@@ -755,13 +755,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>6204</v>
+        <v>6310</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1310</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14">
@@ -772,13 +772,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>6117</v>
+        <v>6204</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1088</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15">
@@ -789,13 +789,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>6103</v>
+        <v>6106</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>997</v>
+        <v>266</v>
       </c>
     </row>
     <row r="16">
@@ -806,13 +806,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>6113</v>
+        <v>6203</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>954</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17">
@@ -823,13 +823,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>6305</v>
+        <v>6308</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>905</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18">
@@ -840,13 +840,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>6307</v>
+        <v>6103</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>855</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19">
@@ -857,13 +857,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>6308</v>
+        <v>6309</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>839</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20">
@@ -874,13 +874,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>6309</v>
+        <v>6302</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>716</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21">
@@ -891,13 +891,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>6110</v>
+        <v>6114</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>667</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22">
@@ -908,13 +908,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>6106</v>
+        <v>6303</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>666</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23">
@@ -925,13 +925,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>6302</v>
+        <v>6111</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>576</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24">
@@ -942,13 +942,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>6105</v>
+        <v>6109</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>525</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25">
@@ -959,13 +959,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>6109</v>
+        <v>6205</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>496</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26">
@@ -976,13 +976,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>6114</v>
+        <v>6201</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>419</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27">
@@ -993,13 +993,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>6310</v>
+        <v>6113</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>380</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28">
@@ -1010,13 +1010,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>6111</v>
+        <v>6105</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>354</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
@@ -1027,13 +1027,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>6304</v>
+        <v>6112</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>313</v>
+        <v>-127</v>
       </c>
     </row>
     <row r="30">
@@ -1050,7 +1050,7 @@
         <v>2023</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>299</v>
+        <v>-170</v>
       </c>
     </row>
     <row r="31">
@@ -1067,7 +1067,7 @@
         <v>2023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>250</v>
+        <v>-193</v>
       </c>
     </row>
     <row r="32">
@@ -1078,13 +1078,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>6112</v>
+        <v>6304</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>202</v>
+        <v>-226</v>
       </c>
     </row>
     <row r="33">
@@ -1095,13 +1095,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>6301</v>
+        <v>6108</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-104</v>
+        <v>-583</v>
       </c>
     </row>
     <row r="34">
@@ -1118,7 +1118,7 @@
         <v>2023</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-9171</v>
+        <v>-1133</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:24</t>
+    <t xml:space="preserve">2026-09-27 22:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:13</t>
+    <t xml:space="preserve">2026-10-01 20:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:54</t>
+    <t xml:space="preserve">2026-10-02 13:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:18</t>
+    <t xml:space="preserve">2026-10-04 08:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:08</t>
+    <t xml:space="preserve">2026-10-05 08:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
